--- a/av/stan_edit.xlsx
+++ b/av/stan_edit.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://utexas-my.sharepoint.com/personal/lh9896_eid_utexas_edu/Documents/Jobs &amp; CV/2025/Lux/presentation/av/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="53" documentId="8_{33F60720-1DD4-1649-8F47-9AF318C3736E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{330CF3C4-BEDC-6141-8A54-9BF94E645A0E}"/>
+  <xr:revisionPtr revIDLastSave="56" documentId="8_{33F60720-1DD4-1649-8F47-9AF318C3736E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D4C1BB9A-F916-1642-8565-73E87BE72892}"/>
   <bookViews>
     <workbookView xWindow="4420" yWindow="760" windowWidth="25820" windowHeight="16320" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -133,7 +133,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -147,6 +147,9 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -164,6 +167,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -520,7 +527,7 @@
       <c r="A8" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="7" t="s">
         <v>10</v>
       </c>
     </row>
